--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487592_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487592_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1791</v>
+        <v>13.025</v>
       </c>
       <c r="E2" t="n">
-        <v>8.943899999999999</v>
+        <v>9.544499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2352</v>
+        <v>3.4805</v>
       </c>
       <c r="G2" t="n">
         <v>8.6981</v>
@@ -610,13 +610,13 @@
         <v>3.4926</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.207</v>
+        <v>-0.3611</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2113</v>
+        <v>-0.6107</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0043</v>
+        <v>0.2496</v>
       </c>
       <c r="V2" t="n">
         <v>2.1657</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7642</v>
+        <v>2.846</v>
       </c>
       <c r="E3" t="n">
         <v>2.0614</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7028</v>
+        <v>0.7846</v>
       </c>
       <c r="G3" t="n">
         <v>1.6908</v>
@@ -688,13 +688,13 @@
         <v>3.8806</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1878</v>
+        <v>-0.106</v>
       </c>
       <c r="T3" t="n">
         <v>-0.4834</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2957</v>
+        <v>0.3774</v>
       </c>
       <c r="V3" t="n">
         <v>-1.6493</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6021</v>
+        <v>2.6928</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6514</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2535</v>
+        <v>3.4443</v>
       </c>
       <c r="G4" t="n">
         <v>-2.0628</v>
@@ -766,13 +766,13 @@
         <v>3.8806</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6046</v>
+        <v>-0.7047</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.032</v>
+        <v>0.1587</v>
       </c>
       <c r="V4" t="n">
         <v>4.3313</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4991</v>
+        <v>1.9168</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4261</v>
+        <v>-0.9266</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9252</v>
+        <v>2.8434</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7979000000000001</v>
@@ -844,13 +844,13 @@
         <v>2.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>0.697</v>
+        <v>0.1147</v>
       </c>
       <c r="T5" t="n">
-        <v>0.305</v>
+        <v>-0.1955</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3919</v>
+        <v>0.3102</v>
       </c>
       <c r="V5" t="n">
         <v>0.6597</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6923</v>
+        <v>1.4565</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5605</v>
+        <v>-0.3603</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2528</v>
+        <v>1.8168</v>
       </c>
       <c r="G6" t="n">
         <v>3.2383</v>
@@ -922,13 +922,13 @@
         <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>0.666</v>
+        <v>0.4301</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3623</v>
+        <v>-0.1621</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0283</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6597</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1045</v>
+        <v>-0.5121</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1454</v>
+        <v>0.3563</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2499</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0069</v>
+        <v>0.291</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008</v>
+        <v>0.5635</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0061</v>
+        <v>-0.2725</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7025</v>
+        <v>0.6591</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0124</v>
+        <v>0.6591</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6901</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6956</v>
+        <v>-0.3681</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0115</v>
+        <v>-0.0956</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.2725</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2618</v>
+        <v>-0.3853</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0924</v>
+        <v>-0.3028</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1694</v>
+        <v>-0.0824</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7029</v>
+        <v>-0.5962</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3563</v>
+        <v>-0.8461</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0592</v>
+        <v>0.2499</v>
       </c>
       <c r="G8" t="n">
-        <v>0.291</v>
+        <v>0.0069</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5635</v>
+        <v>0.0008</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2725</v>
+        <v>0.0061</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6591</v>
+        <v>0.7025</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6591</v>
+        <v>0.0124</v>
       </c>
       <c r="L8" t="n">
+        <v>0.6901</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.6956</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.6840000000000001</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.7761</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5611</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.3681</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.0956</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.2725</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.576</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.3028</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.2732</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.6119</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6958</v>
+        <v>-1.564</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2118</v>
+        <v>-1.8218</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.484</v>
+        <v>0.2578</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7679</v>
+        <v>-1.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1425</v>
+        <v>-1.4072</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9104</v>
+        <v>-0.0929</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0612</v>
+        <v>-1.9614</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0206</v>
+        <v>-1.3347</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0406</v>
+        <v>-0.6267</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.829</v>
+        <v>0.4614</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1219</v>
+        <v>-0.0725</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.951</v>
+        <v>0.5339</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0422</v>
+        <v>0.2181</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3028</v>
+        <v>0.1396</v>
       </c>
       <c r="U9" t="n">
-        <v>0.345</v>
+        <v>0.0785</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7097</v>
+        <v>-1.7865</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.022</v>
+        <v>-1.1117</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3123</v>
+        <v>-0.6748</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5</v>
+        <v>-0.7679</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4072</v>
+        <v>0.1425</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0929</v>
+        <v>-0.9104</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9614</v>
+        <v>0.0612</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3347</v>
+        <v>0.0206</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6267</v>
+        <v>0.0406</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4614</v>
+        <v>-0.829</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0725</v>
+        <v>0.1219</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5339</v>
+        <v>-0.951</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0725</v>
+        <v>-0.0485</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0606</v>
+        <v>-0.2027</v>
       </c>
       <c r="U10" t="n">
-        <v>0.133</v>
+        <v>0.1542</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8255</v>
+        <v>-3.5708</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0796</v>
+        <v>-1.8794</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7459</v>
+        <v>-1.6914</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4288</v>
@@ -1312,13 +1312,13 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6669</v>
+        <v>-0.4122</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0612</v>
+        <v>-0.0067</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1179</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.732299999999999</v>
+        <v>8.732400000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.820800000000002</v>
+        <v>-0.8208000000000029</v>
       </c>
       <c r="F13" t="n">
-        <v>9.553099999999999</v>
+        <v>9.553200000000002</v>
       </c>
       <c r="G13" t="n">
         <v>4.667299999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.117500000000001</v>
+        <v>-2.1175</v>
       </c>
       <c r="I13" t="n">
         <v>6.784800000000001</v>
@@ -1447,10 +1447,10 @@
         <v>3.4357</v>
       </c>
       <c r="L13" t="n">
-        <v>8.953700000000001</v>
+        <v>8.9537</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.722099999999999</v>
+        <v>-7.7221</v>
       </c>
       <c r="N13" t="n">
         <v>-5.552999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>20.3733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7287999999999999</v>
+        <v>-0.7289999999999999</v>
       </c>
       <c r="T13" t="n">
         <v>-2.8995</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1706</v>
+        <v>2.1705</v>
       </c>
       <c r="V13" t="n">
         <v>1.883599999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0911</v>
+        <v>3.6461</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8142</v>
+        <v>2.3147</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2769</v>
+        <v>1.3314</v>
       </c>
       <c r="G14" t="n">
         <v>4.7263</v>
@@ -1546,13 +1546,13 @@
         <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0067</v>
+        <v>-0.4517</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1508</v>
+        <v>-0.6503</v>
       </c>
       <c r="U14" t="n">
-        <v>0.144</v>
+        <v>0.1985</v>
       </c>
       <c r="V14" t="n">
         <v>1.506</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8106</v>
+        <v>2.3017</v>
       </c>
       <c r="E15" t="n">
-        <v>0.929</v>
+        <v>0.8289</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8817</v>
+        <v>1.4728</v>
       </c>
       <c r="G15" t="n">
         <v>1.8169</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3997</v>
+        <v>0.8908</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1222</v>
+        <v>0.0221</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2775</v>
+        <v>0.8687</v>
       </c>
       <c r="V15" t="n">
         <v>0.5642</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>D. MAGANTO LUCAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9489</v>
+        <v>1.1054</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4109</v>
+        <v>-0.1136</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4621</v>
+        <v>1.2191</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3752</v>
+        <v>-0.7095</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5026</v>
+        <v>0.346</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1274</v>
+        <v>-1.0555</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3492</v>
+        <v>0.9107</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6591</v>
+        <v>0.8651</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6901</v>
+        <v>0.0456</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.974</v>
+        <v>-1.6202</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1565</v>
+        <v>-0.5191</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8175</v>
+        <v>-1.1011</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9702</v>
+        <v>2.5224</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1144</v>
+        <v>0.291</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0617</v>
+        <v>-0.3079</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1761</v>
+        <v>0.5989</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2821</v>
+        <v>0.9418</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X16" t="n">
         <v>-0.2821</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MAGANTO LUCAS</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4503</v>
+        <v>0.8849</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7141999999999999</v>
+        <v>1.2107</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1646</v>
+        <v>-0.3258</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7095</v>
+        <v>0.3752</v>
       </c>
       <c r="H17" t="n">
-        <v>0.346</v>
+        <v>0.5026</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0555</v>
+        <v>-0.1274</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9107</v>
+        <v>1.3492</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8651</v>
+        <v>0.6591</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0456</v>
+        <v>0.6901</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6202</v>
+        <v>-0.974</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5191</v>
+        <v>-0.1565</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1011</v>
+        <v>-0.8175</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5224</v>
+        <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3641</v>
+        <v>-0.1783</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9085</v>
+        <v>-0.1385</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5444</v>
+        <v>-0.0398</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9418</v>
+        <v>-0.2821</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-0.2821</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2936</v>
+        <v>-0.1109</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2851</v>
+        <v>-0.9832</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9915</v>
+        <v>0.8723</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8611</v>
+        <v>-1.126</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.9235</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.02</v>
+        <v>-0.2024</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3811</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.795</v>
+        <v>-0.622</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5861</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.48</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0462</v>
+        <v>-0.3015</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4338</v>
+        <v>-0.2836</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3284</v>
+        <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4084</v>
+        <v>0.2092</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5186</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1101</v>
+        <v>0.2933</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6119</v>
+        <v>0.6119</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1179</v>
+        <v>0.6119</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.484</v>
+        <v>-0.4259</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3836</v>
+        <v>0.1841</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8996</v>
+        <v>-0.61</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.126</v>
+        <v>-1.8611</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9235</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2024</v>
+        <v>-1.02</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-1.3811</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.622</v>
+        <v>-0.795</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.5861</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3015</v>
+        <v>-0.0462</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2836</v>
+        <v>-0.4338</v>
       </c>
       <c r="P19" t="n">
-        <v>0.194</v>
+        <v>1.3582</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>2.3284</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.164</v>
+        <v>0.6889</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4845</v>
+        <v>0.4175</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3206</v>
+        <v>0.2714</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6119</v>
+        <v>-0.6119</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6119</v>
+        <v>2.1179</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0072</v>
+        <v>-1.089</v>
       </c>
       <c r="E20" t="n">
         <v>-0.6867</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3206</v>
+        <v>-0.4023</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7771</v>
@@ -2014,13 +2014,13 @@
         <v>0.3881</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0063</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1211</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1149</v>
+        <v>0.0331</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6119</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0652</v>
+        <v>-1.5285</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2493</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3145</v>
+        <v>-2.1782</v>
       </c>
       <c r="G21" t="n">
         <v>0.311</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1821</v>
+        <v>-0.6455</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9085</v>
+        <v>-0.5081</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2736</v>
+        <v>-0.1374</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6119</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2422</v>
+        <v>-5.8329</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7005</v>
+        <v>-4.8006</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5417</v>
+        <v>-1.0323</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9193</v>
@@ -2170,13 +2170,13 @@
         <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2786</v>
+        <v>-0.3121</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.544</v>
+        <v>-0.6441</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8226</v>
+        <v>0.332</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2134</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.5283</v>
+        <v>-7.6834</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.7567</v>
+        <v>-8.1571</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2284</v>
+        <v>0.4737</v>
       </c>
       <c r="G23" t="n">
         <v>-4.5036</v>
@@ -2248,13 +2248,13 @@
         <v>2.5224</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4798</v>
+        <v>0.3247</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2445</v>
+        <v>-0.1559</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2353</v>
+        <v>0.4806</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1761</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.7324</v>
+        <v>-8.732499999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.5532</v>
+        <v>-9.553100000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8208000000000006</v>
+        <v>0.8206999999999998</v>
       </c>
       <c r="G24" t="n">
         <v>-4.667199999999998</v>
@@ -2326,13 +2326,13 @@
         <v>17.4629</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7289000000000003</v>
+        <v>0.7290000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-2.1704</v>
       </c>
       <c r="U24" t="n">
-        <v>2.8995</v>
+        <v>2.8993</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8834</v>
